--- a/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
+++ b/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
@@ -20,20 +20,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Instituição:</t>
   </si>
   <si>
+    <t xml:space="preserve">Unesp</t>
+  </si>
+  <si>
     <t xml:space="preserve">Professor:</t>
   </si>
   <si>
+    <t xml:space="preserve">Lucimar Sasso Alves</t>
+  </si>
+  <si>
     <t xml:space="preserve">Disciplina:</t>
   </si>
   <si>
+    <t xml:space="preserve">Processamento de Imagens</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nome :</t>
   </si>
   <si>
+    <t xml:space="preserve">Felipe Gomes da Silva</t>
+  </si>
+  <si>
     <t xml:space="preserve">N° Dia</t>
   </si>
   <si>
@@ -47,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Apresentação dos discentes, docentes e metodologia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introdução a imagens (digitais), digitalização (amostragem e quantização) e sinais</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -176,60 +191,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -485,233 +504,251 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="75.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="B6" s="8" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="B7" s="8" t="n">
+        <v>46085</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>46078</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="11"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="11"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="11"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="11"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="11"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="11"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="11"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="11"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="11"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="11"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="11"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="9" t="n">
+      <c r="C26" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="10" t="n">
         <f aca="false">SUM(D6:D25)</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
+++ b/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Instituição:</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">Introdução a imagens (digitais), digitalização (amostragem e quantização) e sinais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aula Prática sobre opencv</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -594,9 +597,15 @@
       <c r="A8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
+      <c r="B8" s="8" t="n">
+        <v>46330</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -744,11 +753,11 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">SUM(D6:D25)</f>
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
+++ b/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
@@ -505,7 +505,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.28"/>
@@ -598,7 +598,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>46330</v>
+        <v>46092</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>14</v>
@@ -612,16 +612,22 @@
       <c r="A9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="8" t="n">
+        <v>46099</v>
+      </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
+      <c r="D9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="8" t="n">
+        <v>46106</v>
+      </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
       <c r="E10" s="12"/>
@@ -630,7 +636,9 @@
       <c r="A11" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="8" t="n">
+        <v>46113</v>
+      </c>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
       <c r="E11" s="12"/>
@@ -639,7 +647,9 @@
       <c r="A12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="8" t="n">
+        <v>46120</v>
+      </c>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
       <c r="E12" s="12"/>
@@ -648,7 +658,9 @@
       <c r="A13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="8" t="n">
+        <v>46127</v>
+      </c>
       <c r="C13" s="9"/>
       <c r="D13" s="10"/>
       <c r="E13" s="12"/>
@@ -657,7 +669,9 @@
       <c r="A14" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="8" t="n">
+        <v>46134</v>
+      </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
       <c r="E14" s="12"/>
@@ -666,7 +680,9 @@
       <c r="A15" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" s="8" t="n">
+        <v>46141</v>
+      </c>
       <c r="C15" s="9"/>
       <c r="D15" s="10"/>
       <c r="E15" s="12"/>
@@ -675,7 +691,9 @@
       <c r="A16" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="8" t="n">
+        <v>46148</v>
+      </c>
       <c r="C16" s="9"/>
       <c r="D16" s="10"/>
       <c r="E16" s="12"/>
@@ -684,7 +702,9 @@
       <c r="A17" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="7"/>
+      <c r="B17" s="8" t="n">
+        <v>46155</v>
+      </c>
       <c r="C17" s="9"/>
       <c r="D17" s="10"/>
       <c r="E17" s="12"/>
@@ -693,7 +713,9 @@
       <c r="A18" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="7"/>
+      <c r="B18" s="8" t="n">
+        <v>46162</v>
+      </c>
       <c r="C18" s="9"/>
       <c r="D18" s="10"/>
       <c r="E18" s="12"/>
@@ -702,7 +724,9 @@
       <c r="A19" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="8" t="n">
+        <v>46169</v>
+      </c>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
       <c r="E19" s="12"/>
@@ -711,7 +735,9 @@
       <c r="A20" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="7"/>
+      <c r="B20" s="8" t="n">
+        <v>46176</v>
+      </c>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="12"/>

--- a/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
+++ b/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">Instituição:</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">Aula Prática sobre opencv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relacionamento entre elementos de uma imagem, conectividade e ops</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -598,7 +601,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>46330</v>
+        <v>46092</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>14</v>
@@ -612,18 +615,28 @@
       <c r="A9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="8" t="n">
+        <v>46099</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="8" t="n">
+        <v>46106</v>
+      </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -753,11 +766,11 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">SUM(D6:D25)</f>
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
+++ b/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Instituição:</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t xml:space="preserve">Relacionamento entre elementos de uma imagem, conectividade e ops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualidade da Imagem e Erros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aula Sobre Ruídos, suas formas e análise</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -633,7 +639,9 @@
       <c r="B10" s="8" t="n">
         <v>46106</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>0.33</v>
       </c>
@@ -643,9 +651,15 @@
       <c r="A11" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -766,11 +780,11 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">SUM(D6:D25)</f>
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
+++ b/pages/Cs/7° Semestre/Processamento-de-Imagens/CADERNETA-DE-NOTAS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t xml:space="preserve">Instituição:</t>
   </si>
@@ -74,6 +74,21 @@
   </si>
   <si>
     <t xml:space="preserve">Aula Sobre Ruídos, suas formas e análise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuação aula de ruidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumo sobre slide 7 e 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aula sobre filtros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paralisação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuação aula de filtros</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -83,11 +98,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="d/mmm"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -203,7 +219,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -258,6 +274,18 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -666,54 +694,90 @@
       <c r="A12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="8" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="8" t="n">
+        <v>46127</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="14" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="8" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="8" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
+      <c r="B17" s="8" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="E17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -779,12 +843,12 @@
       <c r="E25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="14" t="s">
-        <v>18</v>
+      <c r="C26" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">SUM(D6:D25)</f>
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
